--- a/E3_para_correr/Análisis de Excels/comparacion_escenarios.xlsx
+++ b/E3_para_correr/Análisis de Excels/comparacion_escenarios.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>283.5983326693117</v>
+        <v>284.0944145483641</v>
       </c>
       <c r="D2" t="n">
-        <v>284.7645157926213</v>
+        <v>284.7112266114859</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4111612509109964</v>
+        <v>0.2171151671886222</v>
       </c>
       <c r="F2" t="n">
-        <v>369.31</v>
+        <v>542.35</v>
       </c>
       <c r="G2" t="n">
-        <v>174660114</v>
+        <v>179259975</v>
       </c>
       <c r="H2" t="n">
         <v>180000000</v>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>226.3351196037666</v>
+        <v>226.3351196141977</v>
       </c>
       <c r="D3" t="n">
         <v>226.3352196141979</v>
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>53.97</v>
+        <v>120.88</v>
       </c>
       <c r="G3" t="n">
         <v>23570812</v>
